--- a/Full-LC-AUTO/data inputs/jeans/Additional-Description-inputs-Shopsy.xlsx
+++ b/Full-LC-AUTO/data inputs/jeans/Additional-Description-inputs-Shopsy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESHAAN\HAKUR\work--fk-tools\Full-LC-AUTO\data inputs\jeans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD43691-38E9-47AC-A54C-9E6E84F97FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE271712-20D1-443B-AC25-7A87EE017EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="62">
   <si>
     <t>kind</t>
   </si>
@@ -200,6 +200,12 @@
   </si>
   <si>
     <t>White Jeans, Men Jeans, Men Cotton Jeans,Denim Pant,White Pant</t>
+  </si>
+  <si>
+    <t>White-Baggy</t>
+  </si>
+  <si>
+    <t>White Baggy Jeans, Men Baggy Jeans, Men Cotton Jeans,Denim Pant,Oversized Pant</t>
   </si>
 </sst>
 </file>
@@ -576,13 +582,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AA7"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="27" width="11.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -665,7 +671,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -748,7 +754,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -831,7 +837,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -914,7 +920,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>48</v>
       </c>
@@ -997,7 +1003,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -1077,6 +1083,89 @@
         <v>43</v>
       </c>
       <c r="AA6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7" t="s">
+        <v>53</v>
+      </c>
+      <c r="N7" t="s">
+        <v>54</v>
+      </c>
+      <c r="O7" t="s">
+        <v>50</v>
+      </c>
+      <c r="P7" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>38</v>
+      </c>
+      <c r="R7" t="s">
+        <v>39</v>
+      </c>
+      <c r="S7" t="s">
+        <v>36</v>
+      </c>
+      <c r="T7" t="s">
+        <v>40</v>
+      </c>
+      <c r="U7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V7" t="s">
+        <v>37</v>
+      </c>
+      <c r="W7" t="s">
+        <v>61</v>
+      </c>
+      <c r="X7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA7" t="s">
         <v>43</v>
       </c>
     </row>
